--- a/input/job.xlsx
+++ b/input/job.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Shalini\MobileAutomation\Talntx_MobileAutomation\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D18753-F2FA-4200-8053-7D2BD345806E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A8D6444-DCC0-476E-B9DC-EC22859154E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{27BC8E43-4EB6-4ED1-99D6-D7D447CC3B0C}"/>
   </bookViews>

--- a/input/job.xlsx
+++ b/input/job.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Shalini\MobileAutomation\Talntx_MobileAutomation\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A8D6444-DCC0-476E-B9DC-EC22859154E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B746BB5-1A2F-4BB1-87E9-749F22512258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{27BC8E43-4EB6-4ED1-99D6-D7D447CC3B0C}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="15375" windowHeight="7785" xr2:uid="{27BC8E43-4EB6-4ED1-99D6-D7D447CC3B0C}"/>
   </bookViews>
   <sheets>
     <sheet name="job" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
     <t>Job</t>
   </si>
   <si>
-    <t>Test02</t>
+    <t>Test change1</t>
   </si>
 </sst>
 </file>
